--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3675,7 +3675,7 @@
         <v>121344495</v>
       </c>
       <c r="B30" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>121344497</v>
       </c>
       <c r="B31" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3672,10 +3672,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344495</v>
+        <v>121344497</v>
       </c>
       <c r="B30" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kopptjärnen, NO om, Vrm</t>
+          <t>Kopptjärnen, SO om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>345576</v>
+        <v>345492</v>
       </c>
       <c r="R30" t="n">
-        <v>6605314</v>
+        <v>6605145</v>
       </c>
       <c r="S30" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,6 +3749,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>S-Årj-0405</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3761,7 +3766,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
+          <t>12 exemplar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344497</v>
+        <v>121344495</v>
       </c>
       <c r="B31" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3827,7 +3832,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3837,17 +3842,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kopptjärnen, SO om, Vrm</t>
+          <t>Kopptjärnen, NO om, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>345492</v>
+        <v>345576</v>
       </c>
       <c r="R31" t="n">
-        <v>6605145</v>
+        <v>6605314</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3869,11 +3874,6 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>S-Årj-0405</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12 exemplar</t>
+          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3675,7 +3675,7 @@
         <v>121344497</v>
       </c>
       <c r="B30" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>121344495</v>
       </c>
       <c r="B31" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3672,10 +3672,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344497</v>
+        <v>121344495</v>
       </c>
       <c r="B30" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kopptjärnen, SO om, Vrm</t>
+          <t>Kopptjärnen, NO om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>345492</v>
+        <v>345576</v>
       </c>
       <c r="R30" t="n">
-        <v>6605145</v>
+        <v>6605314</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,11 +3749,6 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>S-Årj-0405</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3766,7 +3761,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>12 exemplar</t>
+          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344495</v>
+        <v>121344497</v>
       </c>
       <c r="B31" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,7 +3827,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3842,17 +3837,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kopptjärnen, NO om, Vrm</t>
+          <t>Kopptjärnen, SO om, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>345576</v>
+        <v>345492</v>
       </c>
       <c r="R31" t="n">
-        <v>6605314</v>
+        <v>6605145</v>
       </c>
       <c r="S31" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3874,6 +3869,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>S-Årj-0405</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
+          <t>12 exemplar</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3672,7 +3672,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344495</v>
+        <v>121344497</v>
       </c>
       <c r="B30" t="n">
         <v>98098</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kopptjärnen, NO om, Vrm</t>
+          <t>Kopptjärnen, SO om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>345576</v>
+        <v>345492</v>
       </c>
       <c r="R30" t="n">
-        <v>6605314</v>
+        <v>6605145</v>
       </c>
       <c r="S30" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,6 +3749,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>S-Årj-0405</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3761,7 +3766,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
+          <t>12 exemplar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,7 +3797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344497</v>
+        <v>121344495</v>
       </c>
       <c r="B31" t="n">
         <v>98098</v>
@@ -3827,7 +3832,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3837,17 +3842,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kopptjärnen, SO om, Vrm</t>
+          <t>Kopptjärnen, NO om, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>345492</v>
+        <v>345576</v>
       </c>
       <c r="R31" t="n">
-        <v>6605145</v>
+        <v>6605314</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3869,11 +3874,6 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>S-Årj-0405</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12 exemplar</t>
+          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3675,7 +3675,7 @@
         <v>121344497</v>
       </c>
       <c r="B30" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>121344495</v>
       </c>
       <c r="B31" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3672,10 +3672,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344497</v>
+        <v>121344495</v>
       </c>
       <c r="B30" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kopptjärnen, SO om, Vrm</t>
+          <t>Kopptjärnen, NO om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>345492</v>
+        <v>345576</v>
       </c>
       <c r="R30" t="n">
-        <v>6605145</v>
+        <v>6605314</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,11 +3749,6 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>S-Årj-0405</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3766,7 +3761,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>12 exemplar</t>
+          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344495</v>
+        <v>121344497</v>
       </c>
       <c r="B31" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3832,7 +3827,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3842,17 +3837,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kopptjärnen, NO om, Vrm</t>
+          <t>Kopptjärnen, SO om, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>345576</v>
+        <v>345492</v>
       </c>
       <c r="R31" t="n">
-        <v>6605314</v>
+        <v>6605145</v>
       </c>
       <c r="S31" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3874,6 +3869,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>S-Årj-0405</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
+          <t>12 exemplar</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 11148-2024 artfynd.xlsx
+++ b/artfynd/A 11148-2024 artfynd.xlsx
@@ -3672,7 +3672,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344495</v>
+        <v>121344497</v>
       </c>
       <c r="B30" t="n">
         <v>98105</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kopptjärnen, NO om, Vrm</t>
+          <t>Kopptjärnen, SO om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>345576</v>
+        <v>345492</v>
       </c>
       <c r="R30" t="n">
-        <v>6605314</v>
+        <v>6605145</v>
       </c>
       <c r="S30" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3749,6 +3749,11 @@
           <t>Karlanda</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>S-Årj-0405</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3761,7 +3766,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
+          <t>12 exemplar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,7 +3797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344497</v>
+        <v>121344495</v>
       </c>
       <c r="B31" t="n">
         <v>98105</v>
@@ -3827,7 +3832,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3837,17 +3842,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kopptjärnen, SO om, Vrm</t>
+          <t>Kopptjärnen, NO om, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>345492</v>
+        <v>345576</v>
       </c>
       <c r="R31" t="n">
-        <v>6605145</v>
+        <v>6605314</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3869,11 +3874,6 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>S-Årj-0405</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>2024-04-02</t>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12 exemplar</t>
+          <t>9 dellokaler inom polygonen med 1 - 170 ex/dellokal. Den med 170 ex i NV hörnet av polygonen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
